--- a/ig/DM-OCTOBRE-2024/ValueSet-JDV-J238-TypeOffre-ROR.xlsx
+++ b/ig/DM-OCTOBRE-2024/ValueSet-JDV-J238-TypeOffre-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="379">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20240927120000</t>
+    <t>20241025120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-27T12:00:00+01:00</t>
+    <t>2024-10-25T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -378,7 +378,7 @@
     <t>47</t>
   </si>
   <si>
-    <t>Dispositif d'emploi accompagné</t>
+    <t>Plateforme Emploi Accompagné (PEA)</t>
   </si>
   <si>
     <t>48</t>
@@ -931,6 +931,216 @@
   </si>
   <si>
     <t>Equipe Mobile d'Appui à la Scolarisation (EMAS)</t>
+  </si>
+  <si>
+    <t>141</t>
+  </si>
+  <si>
+    <t>Espace Santé Jeune (ESJ)</t>
+  </si>
+  <si>
+    <t>142</t>
+  </si>
+  <si>
+    <t>Equipes Mobiles Santé Précarité (EMSP)</t>
+  </si>
+  <si>
+    <t>143</t>
+  </si>
+  <si>
+    <t>Communauté 360</t>
+  </si>
+  <si>
+    <t>144</t>
+  </si>
+  <si>
+    <t>Equipe Mobile de Psychiatrie de la Personne Âgée</t>
+  </si>
+  <si>
+    <t>145</t>
+  </si>
+  <si>
+    <t>Unité d'addictologie</t>
+  </si>
+  <si>
+    <t>146</t>
+  </si>
+  <si>
+    <t>Unité de prise en charge des brûlés</t>
+  </si>
+  <si>
+    <t>147</t>
+  </si>
+  <si>
+    <t>Unité de sevrage complexe</t>
+  </si>
+  <si>
+    <t>148</t>
+  </si>
+  <si>
+    <t>Unité hospitalière d'allergologie</t>
+  </si>
+  <si>
+    <t>149</t>
+  </si>
+  <si>
+    <t>Unité hospitalière de cardiologie</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>Unité hospitalière de chirurgie orthopédique et traumatologique</t>
+  </si>
+  <si>
+    <t>151</t>
+  </si>
+  <si>
+    <t>Unité hospitalière de chirurgie thoracique et cardiovasculaire</t>
+  </si>
+  <si>
+    <t>152</t>
+  </si>
+  <si>
+    <t>Unité hospitalière de chirurgie vasculaire</t>
+  </si>
+  <si>
+    <t>153</t>
+  </si>
+  <si>
+    <t>Unité hospitalière de chirurgie viscérale et digestive</t>
+  </si>
+  <si>
+    <t>154</t>
+  </si>
+  <si>
+    <t>Unité hospitalière de dermatologie</t>
+  </si>
+  <si>
+    <t>155</t>
+  </si>
+  <si>
+    <t>Unité hospitalière de génétique médicale</t>
+  </si>
+  <si>
+    <t>156</t>
+  </si>
+  <si>
+    <t>Unité hospitalière de gériatrie</t>
+  </si>
+  <si>
+    <t>157</t>
+  </si>
+  <si>
+    <t>Unité hospitalière de gynécologie</t>
+  </si>
+  <si>
+    <t>158</t>
+  </si>
+  <si>
+    <t>Unité hospitalière de médecine vasculaire</t>
+  </si>
+  <si>
+    <t>159</t>
+  </si>
+  <si>
+    <t>Unité hospitalière de néphrologie</t>
+  </si>
+  <si>
+    <t>160</t>
+  </si>
+  <si>
+    <t>Unité hospitalière de neurochirurgie</t>
+  </si>
+  <si>
+    <t>161</t>
+  </si>
+  <si>
+    <t>Unité hospitalière de neurologie</t>
+  </si>
+  <si>
+    <t>162</t>
+  </si>
+  <si>
+    <t>Unité hospitalière de pédiatrie</t>
+  </si>
+  <si>
+    <t>163</t>
+  </si>
+  <si>
+    <t>Unité hospitalière de pneumologie</t>
+  </si>
+  <si>
+    <t>164</t>
+  </si>
+  <si>
+    <t>Unité hospitalière de radiologie</t>
+  </si>
+  <si>
+    <t>165</t>
+  </si>
+  <si>
+    <t>Unité hospitalière de rhumatologie</t>
+  </si>
+  <si>
+    <t>166</t>
+  </si>
+  <si>
+    <t>Unité hospitalière de stomatologie, chirurgie orale et maxillo faciale</t>
+  </si>
+  <si>
+    <t>167</t>
+  </si>
+  <si>
+    <t>Unité hospitalière d'endocrinologie, diabétologie et nutrition</t>
+  </si>
+  <si>
+    <t>168</t>
+  </si>
+  <si>
+    <t>Unité hospitalière des maladies infectieuses et tropicales (MIT)</t>
+  </si>
+  <si>
+    <t>169</t>
+  </si>
+  <si>
+    <t>Unité hospitalière d'hématologie</t>
+  </si>
+  <si>
+    <t>170</t>
+  </si>
+  <si>
+    <t>Unité hospitalière d'hépato-gastro-entérologie (HGE)</t>
+  </si>
+  <si>
+    <t>171</t>
+  </si>
+  <si>
+    <t>Unité hospitalière d'oncologie</t>
+  </si>
+  <si>
+    <t>172</t>
+  </si>
+  <si>
+    <t>Unité hospitalière d'ophtalmologie</t>
+  </si>
+  <si>
+    <t>173</t>
+  </si>
+  <si>
+    <t>Unité hospitalière oto-rhino-laryngologie (ORL)</t>
+  </si>
+  <si>
+    <t>174</t>
+  </si>
+  <si>
+    <t>Unité psychiatrique</t>
+  </si>
+  <si>
+    <t>175</t>
+  </si>
+  <si>
+    <t>Unités de soins palliatifs</t>
   </si>
   <si>
     <t/>
@@ -1209,7 +1419,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B141"/>
+  <dimension ref="A1:B176"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -2333,15 +2543,295 @@
         <v>306</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="B142" t="s" s="2">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="B143" t="s" s="2">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="B144" t="s" s="2">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="B145" t="s" s="2">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="B146" t="s" s="2">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="B147" t="s" s="2">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="B148" t="s" s="2">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="B149" t="s" s="2">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="B150" t="s" s="2">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="B151" t="s" s="2">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="B152" t="s" s="2">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="B153" t="s" s="2">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="B154" t="s" s="2">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="B155" t="s" s="2">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="B156" t="s" s="2">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="B157" t="s" s="2">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="B158" t="s" s="2">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="B159" t="s" s="2">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="B160" t="s" s="2">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="B161" t="s" s="2">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="B162" t="s" s="2">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="B163" t="s" s="2">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="B164" t="s" s="2">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="B165" t="s" s="2">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="B166" t="s" s="2">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="B167" t="s" s="2">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="B168" t="s" s="2">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="B169" t="s" s="2">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="B170" t="s" s="2">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="B171" t="s" s="2">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="B172" t="s" s="2">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="B173" t="s" s="2">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="B174" t="s" s="2">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="B175" t="s" s="2">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="B176" t="s" s="2">
+        <v>378</v>
       </c>
     </row>
   </sheetData>
